--- a/data/trans_bre/IP19C05-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C05-Clase-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,54</t>
+          <t>0,0; 6,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 9,88</t>
+          <t>-2,37; 10,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 0,0</t>
+          <t>-9,69; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 6,04</t>
+          <t>-3,02; 6,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 7,19</t>
+          <t>-4,47; 7,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 0,0</t>
+          <t>-6,05; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 6,51</t>
+          <t>-7,02; 6,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,02</t>
+          <t>0,0; 11,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 0,63</t>
+          <t>-4,32; 0,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 5,09</t>
+          <t>-1,09; 4,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 5,37</t>
+          <t>-1,82; 5,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,98</t>
+          <t>0,0; 7,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 2,81</t>
+          <t>-5,79; 2,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 7,36</t>
+          <t>-1,39; 7,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 0,0</t>
+          <t>-9,01; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,87</t>
+          <t>-1,22; 0,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,74</t>
+          <t>-0,96; 2,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 3,02</t>
+          <t>-0,78; 3,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-44,96; 287,52</t>
+          <t>-46,22; 257,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-37,91; 404,16</t>
+          <t>-43,55; 377,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C05-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C05-Clase-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,74</t>
+          <t>0,0; 5,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 10,64</t>
+          <t>-1,83; 11,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 0,0</t>
+          <t>-10,02; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 6,27</t>
+          <t>-3,04; 6,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 7,53</t>
+          <t>-4,11; 7,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -799,12 +799,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 6,66</t>
+          <t>-6,97; 6,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,64</t>
+          <t>0,0; 10,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 0,62</t>
+          <t>-4,29; 0,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 4,81</t>
+          <t>-1,69; 4,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 5,18</t>
+          <t>-1,67; 5,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-82,01; —</t>
         </is>
       </c>
     </row>
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,28</t>
+          <t>0,0; 8,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 2,75</t>
+          <t>-6,06; 3,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 7,47</t>
+          <t>-1,45; 7,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 0,0</t>
+          <t>-8,96; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,91</t>
+          <t>-1,3; 1,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 2,89</t>
+          <t>-0,95; 2,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 3,0</t>
+          <t>-0,62; 2,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-46,22; 257,2</t>
+          <t>-43,64; 259,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-43,55; 377,21</t>
+          <t>-37,84; 406,76</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C05-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C05-Clase-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,69</t>
+          <t>0,0; 6,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 11,66</t>
+          <t>-1,87; 9,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 0,0</t>
+          <t>-9,99; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 6,41</t>
+          <t>-3,09; 6,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 7,5</t>
+          <t>-4,11; 7,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 0,0</t>
+          <t>-6,08; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 6,65</t>
+          <t>-6,85; 6,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,33</t>
+          <t>0,0; 13,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 0,62</t>
+          <t>-4,85; 0,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 4,56</t>
+          <t>-0,98; 5,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 5,24</t>
+          <t>-1,79; 5,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-82,01; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,94</t>
+          <t>0,0; 7,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 3,15</t>
+          <t>-6,16; 2,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 7,51</t>
+          <t>-1,67; 7,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 0,0</t>
+          <t>-9,08; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,01</t>
+          <t>-1,39; 0,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,54</t>
+          <t>-0,99; 2,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 2,79</t>
+          <t>-0,7; 3,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-43,64; 259,17</t>
+          <t>-44,96; 287,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-37,84; 406,76</t>
+          <t>-37,91; 404,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C05-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C05-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,135 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,15</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3,31</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-3,09</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>205,72%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.153717587097119</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3.308152004484487</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-3.094180816991532</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>2.057208716237472</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,54</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-1,87; 9,88</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-9,99; 0,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-1.867726401666109</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-9.991666885777105</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>6.536430899709922</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>9.87890862168863</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,01</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,68</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>66,79%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>26,93%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,09; 6,04</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-4,11; 7,19</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.01377500414801</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.6811788251292681</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="n">
+        <v>0.6679018100457608</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.2693177542217093</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-1,2</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,34</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,56%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="n">
+        <v>-3.091574987074964</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-4.113440165082858</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-6,08; 0,0</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-6,85; 6,51</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 13,02</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="n">
+        <v>6.036601531709627</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>7.185366119264478</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,34 +739,24 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,0</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,55</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-62,22%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>176,11%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>99,95%</t>
+      <c r="C10" s="5" t="n">
+        <v>-1.203138511927064</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.0543016745114866</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2.342372915566477</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.01556847001243264</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -869,204 +764,118 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-4,85; 0,63</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-0,98; 5,09</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,79; 5,37</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-6.082384101141898</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-6.846759896640448</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>6.507511674772452</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>13.02462072787025</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,6</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-1,54</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,58</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-43,92%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>223,03%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,98</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-6,16; 2,81</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,67; 7,36</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-1.003658818058924</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.400702464981171</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.548271287227333</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.6222233922984304</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>1.761050477991716</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.9994698760669748</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-1,8</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4.851115968932213</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-0.9805938699294547</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.787108698152889</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-9,08; 0,0</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.6253539815907877</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>5.090126575050797</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>5.368061468318523</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1074,77 +883,205 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,18</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,75</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,95</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-21,61%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>41,39%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>61,14%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>1.596605433229361</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-1.542764979633937</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>2.576099591545784</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.439201396593303</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>2.230267642904814</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-1,39; 0,87</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-0,99; 2,74</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-0,7; 3,02</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-44,96; 287,52</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-37,91; 404,16</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-6.157219511240241</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.670548779998374</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>7.977878307239145</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.809239851090538</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>7.363250553020115</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-1.802069738871635</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G19" s="6" t="inlineStr"/>
+      <c r="H19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-9.076326067385722</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.1794210303542143</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.7504797326211815</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.9454288952899774</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>-0.2161012034448189</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.4138737617726358</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.6114237274465095</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-1.394516471552373</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.9932564911850057</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.7049046241393747</v>
+      </c>
+      <c r="F23" s="6" t="inlineStr"/>
+      <c r="G23" s="6" t="n">
+        <v>-0.4495548779065367</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.3791049202439755</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.8689678037547501</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>2.737144760973037</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>3.024823939909439</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr"/>
+      <c r="G24" s="6" t="n">
+        <v>2.875242422962969</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>4.041630742509384</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1153,15 +1090,15 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
